--- a/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -73,7 +73,7 @@
     <t>{.warehouseLocationCode}</t>
   </si>
   <si>
-    <t>{.priority}</t>
+    <t>{.sort}</t>
   </si>
   <si>
     <t>{.statusName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -61,7 +61,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.enaNo}</t>
+    <t>{.eanNo}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>sku编码</t>
   </si>
@@ -37,9 +37,6 @@
     <t>产品名称</t>
   </si>
   <si>
-    <t>EAN码</t>
-  </si>
-  <si>
     <t>所属仓库</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
   </si>
   <si>
     <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.eanNo}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>
@@ -1049,18 +1043,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
-    <col min="5" max="5" width="18.75" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1070,13 +1064,13 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1084,35 +1078,29 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1126,7 +1114,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -1138,7 +1126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
